--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -852,11 +852,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Date de l'observation :
+    <t>Date de l'observation :
  L'élément  doit être présent dans une observation autonome (c'est-à-dire une observation qui n'apparait pas dans un organizer qui contient déjà un effectiveTime) et doit contenir la date de l'observation clinique. 
  Cet élément doit être précis à la date du jour. 
  Si la date et l'heure sont inconnues, cet élément doit l'indiquer à l'aide d'un attribut nullFlavor. 
- La date doit être enregistrée à l'aide du type de données approprié (pour une date précise ou pour un intervalle contenant un élément low et un élément high). </t>
+ La date doit être enregistrée à l'aide du type de données approprié (pour une date précise ou pour un intervalle contenant un élément low et un élément high).</t>
   </si>
   <si>
     <t>Date de l'observation</t>
@@ -882,7 +882,7 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>
@@ -919,7 +919,7 @@
     <t>Observation.targetSiteCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Localisation anatomique : Terminologie : SNOMED CT (2.16.840.1.113883.6.96) </t>
+    <t>Localisation anatomique : Terminologie : SNOMED CT (2.16.840.1.113883.6.96)</t>
   </si>
   <si>
     <t>Localisation anatomique</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-simple-observation.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-simple-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
